--- a/ExcelTool/LubanTools/DataTables/Datas/PopularityData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PopularityData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E5DCED-688B-401F-A437-D146AD61116B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C527D21B-DD5A-457E-8D30-E9408073A8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="6560" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15460" yWindow="7980" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TbLocalzationKeyData#spe=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,13 +79,16 @@
   </si>
   <si>
     <t>CharacterNames+Character_NPC_03</t>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData#sep=+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +98,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -122,17 +129,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{3CE423E5-BEE3-4B03-92DA-23A5A8A840E8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -438,11 +450,11 @@
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -450,13 +462,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -464,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>15</v>
@@ -475,7 +487,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1">
         <v>200</v>
@@ -486,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1">
         <v>1500</v>
